--- a/data/trans_orig/IQ2601_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ2601_R2-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>54983</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>47465</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>61811</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>65,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>56,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>73,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>61106</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53963</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67873</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>53091</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>68190</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>68,72%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>60,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>76,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>54983</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>48025</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>62166</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>65,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105829</t>
+          <t>104471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125545</t>
+          <t>125124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>29284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>22456</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36802</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>26,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27819</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21052</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34962</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20735</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35834</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>31,28%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>29284</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22101</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36242</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>34,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>48068</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>68721</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88925</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>296470</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>279690</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>312998</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>63,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>59,67%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>66,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>404</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>266875</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>252123</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>282234</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>251006</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>282137</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>65,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,04%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>69,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>296470</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>278816</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>311097</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>63,25%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>540098</t>
+          <t>541436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>586744</t>
+          <t>584544</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>172280</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>155752</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>189060</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>36,75%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>33,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>40,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>139539</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>124180</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>154291</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>124277</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>155408</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>34,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30,55%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>172280</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>157653</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>189934</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288420</t>
+          <t>290620</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>335066</t>
+          <t>333728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>468750</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>468750</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>468750</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>406414</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>707</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>468750</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>468750</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>468750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>110294</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>100861</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>118347</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>71,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>65,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>123054</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>113123</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>132485</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>112775</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>132375</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>72,67%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>66,81%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>78,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>110294</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>101084</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>119049</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>71,84%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220714</t>
+          <t>220781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246241</t>
+          <t>245555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43230</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35177</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>52663</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>34,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>46269</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>36838</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56200</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>36948</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>56548</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>27,33%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>21,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>33,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>43230</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>34475</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>52440</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76606</t>
+          <t>77292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>102133</t>
+          <t>102066</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>153524</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>169323</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>153524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,107 +1752,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>461747</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>440182</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>482109</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>65,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>68,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>451037</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>432164</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>469291</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>433101</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>470992</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>65,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>70,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>461747</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>442131</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>482357</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>65,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>70,86%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>912784</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>881314</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>936123</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>66,57%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>64,27%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>68,27%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>912784</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>884503</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>938823</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>66,57%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>64,51%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -1865,107 +1865,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>244794</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>224432</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>266359</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>34,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>213626</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>195372</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>232499</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>193671</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>231562</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>29,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>34,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>244794</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>224184</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>264410</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>29,14%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>34,84%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>458420</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>435081</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>489890</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>33,43%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>31,73%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>37,42%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>458420</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>432381</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>486701</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>33,43%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>31,53%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>706541</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>706541</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>706541</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>706541</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>706541</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>706541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33925</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>26480</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>42373</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>49,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>41159</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32547</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>48811</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32998</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>48594</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>45,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,16%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33925</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>26212</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>41116</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>39,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65101</t>
+          <t>64029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86481</t>
+          <t>86673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>51639</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>43191</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59084</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>60,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>69,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48961</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>41309</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57573</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41526</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57122</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>54,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>45,84%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>63,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>51639</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>44448</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>59352</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>60,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89203</t>
+          <t>89011</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110583</t>
+          <t>111655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85564</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90120</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85564</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>234781</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>216418</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>252716</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>49,28%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45,42%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>53,04%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>219987</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>203527</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>238450</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>201770</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>237767</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>50,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>46,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>234781</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>215798</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>251308</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>49,28%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>428864</t>
+          <t>427570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>480461</t>
+          <t>478803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>241670</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>223735</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>260033</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>50,72%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>309</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>218056</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>199593</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>234516</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>200276</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>236273</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>49,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>241670</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>225143</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>260653</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>50,72%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434034</t>
+          <t>435692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>485631</t>
+          <t>486925</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,25%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476451</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476451</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476451</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>633</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>438043</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>438043</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>438043</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476451</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476451</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>87507</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77878</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>98227</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,54%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>60,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>99962</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>89977</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>109434</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>89452</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>109824</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,62%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>56,37%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>87507</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>76812</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>97788</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,54%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>171422</t>
+          <t>172874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>201330</t>
+          <t>202005</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75929</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>65209</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>85558</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,46%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>39,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>52,35%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>59658</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>50186</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>69643</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>49796</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>70168</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,38%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,63%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75929</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65648</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86624</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,46%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121726</t>
+          <t>121051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151634</t>
+          <t>150182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>163436</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>159620</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>159620</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>159620</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>163436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>356214</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>333900</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>380035</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>49,1%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>46,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,39%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>525</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>361108</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>337344</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>381526</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>340065</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>382882</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>52,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>49,05%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>356214</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>334736</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>379823</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>49,1%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>685372</t>
+          <t>685404</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>751256</t>
+          <t>750463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>369237</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>345416</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>391551</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,61%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,97%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>465</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>326675</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>306257</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>350439</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>304901</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>347718</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>47,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>44,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>369237</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>345628</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>390715</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>50,9%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661978</t>
+          <t>662771</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727862</t>
+          <t>727830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>725451</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>725451</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>725451</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>990</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>687783</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>687783</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>687783</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1034</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>725451</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>725451</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>725451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>42743</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35676</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48997</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>52,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>71,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>38076</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>32072</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44510</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>32055</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44185</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>64,75%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>42743</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>35864</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>62,29%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>71026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89580</t>
+          <t>90421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,96%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25871</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>32938</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20732</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14298</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>26736</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26753</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>35,25%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25871</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19228</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>32750</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>37001</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>56396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>58808</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,67 +4272,67 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>316906</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>298409</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>334070</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>65,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>68,67%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>302667</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>286292</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>320377</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>285959</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>318643</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>64,97%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>61,45%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68,77%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>316906</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>298379</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>332748</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>593962</t>
+          <t>596223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>643728</t>
+          <t>641990</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -4385,64 +4385,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>169588</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>152424</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>188085</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>34,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>31,33%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>163205</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>145495</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>179580</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>147229</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>179913</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>35,03%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38,55%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>169588</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>153746</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>188115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>31,6%</t>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>308638</t>
+          <t>310376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358404</t>
+          <t>356143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,4%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>486494</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>703</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>465872</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>486494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>114699</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>103953</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>124932</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>57,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>68,56%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>103523</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>92164</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>113350</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>93897</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>115061</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61,31%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>114699</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>103575</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>125097</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>202956</t>
+          <t>203916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>233327</t>
+          <t>234431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>67524</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>57291</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>78270</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65337</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>76696</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53799</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74963</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,69%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>67524</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>57126</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>78648</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>117756</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148127</t>
+          <t>147167</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,92%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>182223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>168860</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>182223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>474348</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>451187</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>497019</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>61,19%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>67,41%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>444266</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>424179</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>463217</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>422565</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>463696</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>64,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>474348</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>453926</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>495865</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>64,33%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>887063</t>
+          <t>890646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>948036</t>
+          <t>946107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>262984</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>240313</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>286145</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>35,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>32,59%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>374</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>249274</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>230323</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>269361</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>229844</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>270975</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>35,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>262984</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>241467</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>283406</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>35,67%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>482835</t>
+          <t>484764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>543808</t>
+          <t>540225</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8548</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10654</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>68,97%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>44,28%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>85,97%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9090</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5956</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10322</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>56,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>7326</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>18162</t>
+          <t>14730</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>17489</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>87,11%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3845</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6905</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>31,03%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,03%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1543</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4677</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14,52%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>43,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>1501</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>357</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12393</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10633</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>88764</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>79372</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>97011</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>72,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>64,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>78,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>58860</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>51456</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>65658</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>66,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58,36%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>74,46%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>96605</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86936</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106138</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>155465</t>
+          <t>145913</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142723</t>
+          <t>134665</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166667</t>
+          <t>156681</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>34124</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>25877</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43516</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>35,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>29314</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>22516</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36718</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,25%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41,64%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>36614</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>22646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46283</t>
+          <t>37628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>65928</t>
+          <t>64195</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>53427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78670</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>122888</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>88174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>88174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>88174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133219</t>
+          <t>87220</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>221393</t>
+          <t>210108</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>221393</t>
+          <t>210108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>221393</t>
+          <t>210108</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33566</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27319</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37932</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>77,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>88,04%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31035</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25522</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35399</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>71,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>59,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>81,85%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34569</t>
+          <t>30975</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>35564</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>65605</t>
+          <t>64540</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57359</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71892</t>
+          <t>70589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9518</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5152</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>15765</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11,96%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>36,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12213</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7849</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17726</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28,24%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>40,99%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16442</t>
+          <t>17939</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22198</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>16149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43084</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>43248</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44721</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>87970</t>
+          <t>86738</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>119578</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>140854</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>67,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>78,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>98984</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>89370</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>107503</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>69,68%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>62,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>140248</t>
+          <t>94305</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>128483</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>152196</t>
+          <t>103047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>239232</t>
+          <t>225183</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223897</t>
+          <t>211054</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>252531</t>
+          <t>238878</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,37%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47487</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>37511</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>58787</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>26,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>32,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>43071</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34552</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>52685</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>30,32%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>37,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51522</t>
+          <t>44252</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39574</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63287</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>94592</t>
+          <t>91739</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81293</t>
+          <t>78044</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>109927</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>142055</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>138557</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>333824</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
